--- a/public/exports-60-250/29189846.xlsx
+++ b/public/exports-60-250/29189846.xlsx
@@ -8464,7 +8464,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368606</t>
+          <t xml:space="preserve">311284535</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
